--- a/StructureDefinition-ng-mnch-referral-bundle.xlsx
+++ b/StructureDefinition-ng-mnch-referral-bundle.xlsx
@@ -51,7 +51,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>2-NGReferral MNCH Transaction Bundle</t>
+    <t>Bundle NG Referral MNCH</t>
   </si>
   <si>
     <t>Status</t>
